--- a/Tuition.xlsx
+++ b/Tuition.xlsx
@@ -4,10 +4,18 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Subjects" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Members" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Payments" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Members" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Logs" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Logs" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Subjects" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="CalendarEvents" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Teachers" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="Students" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="Enrollments" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="ChatHistory" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="ChatbotFeedback" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="Pricing" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="Attendance" sheetId="13" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,15 +23,123 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
-  <si>
-    <t>LOG-1771047675521</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>Initialize sheets error: Exception: The number of columns in the data does not match the number of columns in the range. The data has 12 but the range has 26.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
+  <si>
+    <t>member_id</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>ic_number</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>postcode</t>
+  </si>
+  <si>
+    <t>subjects</t>
+  </si>
+  <si>
+    <t>tuition_type</t>
+  </si>
+  <si>
+    <t>enrollment_date</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>password_hash</t>
+  </si>
+  <si>
+    <t>parent_name</t>
+  </si>
+  <si>
+    <t>parent_phone</t>
+  </si>
+  <si>
+    <t>parent_email</t>
+  </si>
+  <si>
+    <t>emergency_contact</t>
+  </si>
+  <si>
+    <t>school_name</t>
+  </si>
+  <si>
+    <t>current_level</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>payment_id</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>payment_date</t>
+  </si>
+  <si>
+    <t>transaction_id</t>
+  </si>
+  <si>
+    <t>payment_method</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>package_name</t>
+  </si>
+  <si>
+    <t>receipt_url</t>
+  </si>
+  <si>
+    <t>log_id</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>LOG-1771057156706</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>All sheets initialized successfully</t>
   </si>
   <si>
     <t>initializeSheets</t>
@@ -32,10 +148,145 @@
     <t>System</t>
   </si>
   <si>
-    <t>LOG-1771047728411</t>
-  </si>
-  <si>
-    <t>Initialize sheets error: Exception: The number of columns in the data does not match the number of columns in the range. The data has 8 but the range has 26.</t>
+    <t>subject_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>base_price</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>event_id</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>subject</t>
+  </si>
+  <si>
+    <t>teacher_id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>start_datetime</t>
+  </si>
+  <si>
+    <t>end_datetime</t>
+  </si>
+  <si>
+    <t>students</t>
+  </si>
+  <si>
+    <t>max_students</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>recurring</t>
+  </si>
+  <si>
+    <t>repeat_until</t>
+  </si>
+  <si>
+    <t>repeat_days</t>
+  </si>
+  <si>
+    <t>created_by</t>
+  </si>
+  <si>
+    <t>qualification</t>
+  </si>
+  <si>
+    <t>experience</t>
+  </si>
+  <si>
+    <t>photo_url</t>
+  </si>
+  <si>
+    <t>student_id</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>enrollment_id</t>
+  </si>
+  <si>
+    <t>student_data</t>
+  </si>
+  <si>
+    <t>parent_data</t>
+  </si>
+  <si>
+    <t>academic_data</t>
+  </si>
+  <si>
+    <t>payment_data</t>
+  </si>
+  <si>
+    <t>submitted_at</t>
+  </si>
+  <si>
+    <t>processed_at</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>session_id</t>
+  </si>
+  <si>
+    <t>sender</t>
+  </si>
+  <si>
+    <t>context</t>
+  </si>
+  <si>
+    <t>rating</t>
+  </si>
+  <si>
+    <t>feedback</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>package_id</t>
+  </si>
+  <si>
+    <t>subjects_count</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>features</t>
+  </si>
+  <si>
+    <t>is_popular</t>
+  </si>
+  <si>
+    <t>attendance_id</t>
+  </si>
+  <si>
+    <t>check_in_time</t>
+  </si>
+  <si>
+    <t>check_out_time</t>
+  </si>
+  <si>
+    <t>marked_by</t>
   </si>
 </sst>
 </file>
@@ -45,10 +296,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -72,14 +329,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -94,6 +354,22 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -107,6 +383,22 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -319,13 +611,278 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.75"/>
+    <col customWidth="1" min="2" max="2" width="8.63"/>
+    <col customWidth="1" min="3" max="3" width="6.0"/>
+    <col customWidth="1" min="4" max="4" width="7.63"/>
+    <col customWidth="1" min="5" max="5" width="6.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.75"/>
+    <col customWidth="1" min="2" max="2" width="8.63"/>
+    <col customWidth="1" min="3" max="3" width="5.25"/>
+    <col customWidth="1" min="4" max="4" width="7.63"/>
+    <col customWidth="1" min="5" max="5" width="6.25"/>
+    <col customWidth="1" min="6" max="6" width="6.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="9.25"/>
+    <col customWidth="1" min="2" max="2" width="4.38"/>
+    <col customWidth="1" min="3" max="3" width="5.0"/>
+    <col customWidth="1" min="4" max="4" width="12.0"/>
+    <col customWidth="1" min="5" max="5" width="4.63"/>
+    <col customWidth="1" min="6" max="6" width="7.0"/>
+    <col customWidth="1" min="7" max="7" width="8.5"/>
+    <col customWidth="1" min="8" max="8" width="7.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.25"/>
+    <col customWidth="1" min="2" max="2" width="7.0"/>
+    <col customWidth="1" min="3" max="3" width="8.5"/>
+    <col customWidth="1" min="4" max="4" width="5.5"/>
+    <col customWidth="1" min="5" max="5" width="11.38"/>
+    <col customWidth="1" min="6" max="6" width="12.38"/>
+    <col customWidth="1" min="7" max="7" width="5.0"/>
+    <col customWidth="1" min="8" max="8" width="8.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="9.13"/>
+    <col customWidth="1" min="2" max="2" width="8.13"/>
+    <col customWidth="1" min="3" max="3" width="8.5"/>
+    <col customWidth="1" min="4" max="4" width="5.0"/>
+    <col customWidth="1" min="5" max="5" width="5.5"/>
+    <col customWidth="1" min="6" max="6" width="6.75"/>
+    <col customWidth="1" min="7" max="7" width="3.63"/>
+    <col customWidth="1" min="8" max="8" width="4.63"/>
+    <col customWidth="1" min="9" max="9" width="7.75"/>
+    <col customWidth="1" min="10" max="10" width="7.13"/>
+    <col customWidth="1" min="11" max="11" width="9.5"/>
+    <col customWidth="1" min="12" max="12" width="12.75"/>
+    <col customWidth="1" min="13" max="13" width="5.5"/>
+    <col customWidth="1" min="14" max="14" width="12.25"/>
+    <col customWidth="1" min="15" max="15" width="10.38"/>
+    <col customWidth="1" min="16" max="16" width="10.88"/>
+    <col customWidth="1" min="17" max="17" width="10.38"/>
+    <col customWidth="1" min="18" max="18" width="15.25"/>
+    <col customWidth="1" min="19" max="19" width="10.63"/>
+    <col customWidth="1" min="20" max="20" width="10.38"/>
+    <col customWidth="1" min="21" max="21" width="8.63"/>
+    <col customWidth="1" min="22" max="22" width="9.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -336,7 +893,59 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="39.0"/>
+    <col customWidth="1" min="2" max="2" width="9.13"/>
+    <col customWidth="1" min="3" max="3" width="10.25"/>
+    <col customWidth="1" min="4" max="4" width="13.88"/>
+    <col customWidth="1" min="5" max="5" width="17.75"/>
+    <col customWidth="1" min="6" max="6" width="16.88"/>
+    <col customWidth="1" min="7" max="7" width="5.5"/>
+    <col customWidth="1" min="8" max="8" width="9.13"/>
+    <col customWidth="1" min="9" max="9" width="11.88"/>
+    <col customWidth="1" min="10" max="10" width="7.13"/>
+    <col customWidth="1" min="11" max="12" width="8.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -347,7 +956,56 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="5.25"/>
+    <col customWidth="1" min="2" max="2" width="8.75"/>
+    <col customWidth="1" min="3" max="3" width="4.38"/>
+    <col customWidth="1" min="4" max="4" width="7.63"/>
+    <col customWidth="1" min="5" max="5" width="6.88"/>
+    <col customWidth="1" min="6" max="6" width="4.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46067.68005446759</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -358,45 +1016,300 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.38"/>
+    <col customWidth="1" min="2" max="2" width="5.0"/>
+    <col customWidth="1" min="3" max="3" width="4.5"/>
+    <col customWidth="1" min="4" max="4" width="4.38"/>
+    <col customWidth="1" min="5" max="5" width="8.88"/>
+    <col customWidth="1" min="6" max="6" width="9.13"/>
+    <col customWidth="1" min="7" max="7" width="7.38"/>
+    <col customWidth="1" min="8" max="8" width="8.63"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>46067.570318530095</v>
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="7.0"/>
+    <col customWidth="1" min="2" max="2" width="3.75"/>
+    <col customWidth="1" min="3" max="3" width="6.25"/>
+    <col customWidth="1" min="4" max="4" width="8.5"/>
+    <col customWidth="1" min="5" max="5" width="4.13"/>
+    <col customWidth="1" min="6" max="6" width="11.63"/>
+    <col customWidth="1" min="7" max="7" width="10.88"/>
+    <col customWidth="1" min="8" max="8" width="6.88"/>
+    <col customWidth="1" min="9" max="9" width="7.38"/>
+    <col customWidth="1" min="10" max="10" width="11.13"/>
+    <col customWidth="1" min="11" max="11" width="9.13"/>
+    <col customWidth="1" min="12" max="12" width="7.75"/>
+    <col customWidth="1" min="13" max="13" width="7.63"/>
+    <col customWidth="1" min="14" max="14" width="9.5"/>
+    <col customWidth="1" min="15" max="15" width="9.75"/>
+    <col customWidth="1" min="16" max="16" width="5.5"/>
+    <col customWidth="1" min="17" max="17" width="8.88"/>
+    <col customWidth="1" min="18" max="18" width="8.63"/>
+    <col customWidth="1" min="19" max="19" width="9.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.5"/>
+    <col customWidth="1" min="2" max="3" width="5.0"/>
+    <col customWidth="1" min="4" max="4" width="5.5"/>
+    <col customWidth="1" min="5" max="5" width="7.13"/>
+    <col customWidth="1" min="6" max="6" width="10.0"/>
+    <col customWidth="1" min="7" max="7" width="9.0"/>
+    <col customWidth="1" min="8" max="8" width="5.5"/>
+    <col customWidth="1" min="9" max="9" width="7.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.5"/>
+    <col customWidth="1" min="2" max="2" width="5.0"/>
+    <col customWidth="1" min="3" max="3" width="8.5"/>
+    <col customWidth="1" min="4" max="4" width="5.0"/>
+    <col customWidth="1" min="5" max="5" width="5.5"/>
+    <col customWidth="1" min="6" max="6" width="5.75"/>
+    <col customWidth="1" min="7" max="7" width="4.38"/>
+    <col customWidth="1" min="8" max="8" width="7.13"/>
+    <col customWidth="1" min="9" max="9" width="10.38"/>
+    <col customWidth="1" min="10" max="10" width="10.88"/>
+    <col customWidth="1" min="11" max="11" width="5.5"/>
+    <col customWidth="1" min="12" max="12" width="12.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46067.57093068287</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="10.88"/>
+    <col customWidth="1" min="2" max="2" width="10.38"/>
+    <col customWidth="1" min="3" max="3" width="9.63"/>
+    <col customWidth="1" min="4" max="4" width="12.0"/>
+    <col customWidth="1" min="5" max="5" width="11.25"/>
+    <col customWidth="1" min="6" max="6" width="5.5"/>
+    <col customWidth="1" min="7" max="7" width="10.5"/>
+    <col customWidth="1" min="8" max="8" width="10.63"/>
+    <col customWidth="1" min="9" max="9" width="5.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
